--- a/product_selector_out/STM32H742.xlsx
+++ b/product_selector_out/STM32H742.xlsx
@@ -9806,7 +9806,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min reads '1.62(1)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -9872,7 +9872,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min reads '1.62(1)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -9938,7 +9938,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min reads '1.62(1)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -10004,7 +10004,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min reads '1.62(1)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -10070,7 +10070,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min reads '1.62(1)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -10136,7 +10136,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min reads '1.62(1)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -10202,7 +10202,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min reads '1.62(1)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -10268,7 +10268,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min reads '1.62(1)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -10334,7 +10334,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min reads '1.62(1)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -10400,7 +10400,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min reads '1.62(1)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -10466,7 +10466,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min reads '1.62(1)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -10532,7 +10532,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min reads '1.62(1)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>

--- a/product_selector_out/STM32H742.xlsx
+++ b/product_selector_out/STM32H742.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO23"/>
+  <dimension ref="A1:BP23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.79296875" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,8 @@
     <col width="21.765625" customWidth="1" min="64" max="64"/>
     <col width="18" customWidth="1" min="65" max="65"/>
     <col width="18" customWidth="1" min="66" max="66"/>
-    <col width="52" customWidth="1" min="67" max="67"/>
+    <col width="18" customWidth="1" min="67" max="67"/>
+    <col width="52" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -907,6 +908,11 @@
         </is>
       </c>
       <c r="BO10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BP10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -1004,6 +1010,7 @@
       <c r="BM11" s="2" t="n"/>
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
+      <c r="BP11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1338,6 +1345,11 @@
       </c>
       <c r="BO12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h742ag.pdf</t>
         </is>
       </c>
@@ -1675,6 +1687,11 @@
       </c>
       <c r="BO13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h742ag.pdf</t>
         </is>
       </c>
@@ -2012,6 +2029,11 @@
       </c>
       <c r="BO14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h742ag.pdf</t>
         </is>
       </c>
@@ -2349,6 +2371,11 @@
       </c>
       <c r="BO15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h742ag.pdf</t>
         </is>
       </c>
@@ -2686,6 +2713,11 @@
       </c>
       <c r="BO16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h742ag.pdf</t>
         </is>
       </c>
@@ -3023,6 +3055,11 @@
       </c>
       <c r="BO17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h742ag.pdf</t>
         </is>
       </c>
@@ -3360,6 +3397,11 @@
       </c>
       <c r="BO18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h742ag.pdf</t>
         </is>
       </c>
@@ -3697,6 +3739,11 @@
       </c>
       <c r="BO19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h742ag.pdf</t>
         </is>
       </c>
@@ -4034,6 +4081,11 @@
       </c>
       <c r="BO20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h742ag.pdf</t>
         </is>
       </c>
@@ -4371,6 +4423,11 @@
       </c>
       <c r="BO21" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h742ag.pdf</t>
         </is>
       </c>
@@ -4708,6 +4765,11 @@
       </c>
       <c r="BO22" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h742ag.pdf</t>
         </is>
       </c>
@@ -5045,12 +5107,17 @@
       </c>
       <c r="BO23" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP23" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h742ag.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="66">
+  <mergeCells count="67">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -5073,12 +5140,14 @@
     <mergeCell ref="Q10:Q11"/>
     <mergeCell ref="AR10:AR11"/>
     <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="A9:BP9"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="A1:BP8"/>
     <mergeCell ref="AV10:AV11"/>
     <mergeCell ref="BB10:BB11"/>
+    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BD10:BD11"/>
     <mergeCell ref="BM10:BM11"/>
-    <mergeCell ref="BD10:BD11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -5093,9 +5162,8 @@
     <mergeCell ref="BH10:BH11"/>
     <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
-    <mergeCell ref="A1:BO8"/>
+    <mergeCell ref="BP10:BP11"/>
     <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="A9:BO9"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="I10:I11"/>
     <mergeCell ref="AL10:AL11"/>
@@ -5143,7 +5211,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO23"/>
+  <dimension ref="A1:BP23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5213,6 +5281,7 @@
     <col width="16" customWidth="1" min="65" max="65"/>
     <col width="16" customWidth="1" min="66" max="66"/>
     <col width="16" customWidth="1" min="67" max="67"/>
+    <col width="16" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5556,6 +5625,11 @@
         </is>
       </c>
       <c r="BO10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BP10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -5653,6 +5727,7 @@
       <c r="BM11" s="2" t="n"/>
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
+      <c r="BP11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -5985,7 +6060,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO12" s="6" t="inlineStr">
+      <c r="BO12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6322,7 +6402,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO13" s="6" t="inlineStr">
+      <c r="BO13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6659,7 +6744,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO14" s="6" t="inlineStr">
+      <c r="BO14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6996,7 +7086,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO15" s="6" t="inlineStr">
+      <c r="BO15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7333,7 +7428,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO16" s="6" t="inlineStr">
+      <c r="BO16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7670,7 +7770,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO17" s="6" t="inlineStr">
+      <c r="BO17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8007,7 +8112,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO18" s="6" t="inlineStr">
+      <c r="BO18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8344,7 +8454,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO19" s="6" t="inlineStr">
+      <c r="BO19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8681,7 +8796,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO20" s="6" t="inlineStr">
+      <c r="BO20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9018,7 +9138,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO21" s="6" t="inlineStr">
+      <c r="BO21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9355,7 +9480,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO22" s="6" t="inlineStr">
+      <c r="BO22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9692,7 +9822,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO23" s="6" t="inlineStr">
+      <c r="BO23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP23" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9700,8 +9835,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BO9"/>
-    <mergeCell ref="A1:BO8"/>
+    <mergeCell ref="A1:BP8"/>
+    <mergeCell ref="A9:BP9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
